--- a/public/uploads/invoice/ERS05071-Invoice1.xlsx
+++ b/public/uploads/invoice/ERS05071-Invoice1.xlsx
@@ -52,7 +52,7 @@
     <t>Lakeview Road Bridge</t>
   </si>
   <si>
-    <t>02/20/2026</t>
+    <t>02/21/2026</t>
   </si>
   <si>
     <t>1258 Willingham Dr</t>
@@ -172,7 +172,7 @@
     <t>AMOUNT EARNED LESS RETAINAGE:</t>
   </si>
   <si>
-    <t>CURRENT RETAINAGE @ 5.00%</t>
+    <t>CURRENT RETAINAGE @ 10.00%</t>
   </si>
   <si>
     <t>LESS RETAINAGE</t>
@@ -2332,10 +2332,10 @@
         <v>58.0</v>
       </c>
       <c r="G17" s="119">
-        <v>1500.0</v>
+        <v>1.0</v>
       </c>
       <c r="H17" s="118">
-        <v>87000.0</v>
+        <v>58.0</v>
       </c>
       <c r="I17" s="119">
         <v>889.63</v>
@@ -2868,17 +2868,17 @@
         <v>0</v>
       </c>
       <c r="O25" s="119">
-        <v>0.950977</v>
+        <v>1.0</v>
       </c>
       <c r="P25" s="118">
-        <v>-1734.33999999999992</v>
+        <v>-1823.75</v>
       </c>
       <c r="Q25" s="120"/>
       <c r="R25" s="119">
-        <v>0.950977</v>
+        <v>1.0</v>
       </c>
       <c r="S25" s="118">
-        <v>-1734.33999999999992</v>
+        <v>-1823.75</v>
       </c>
       <c r="T25" s="1"/>
       <c r="U25" s="57"/>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="H33" s="92">
         <f>SUM(H16:H32)</f>
-        <v>268718.25</v>
+        <v>181776.25</v>
       </c>
       <c r="I33" s="93" t="s">
         <v>57</v>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="P33" s="100">
         <f>SUM(P16:P32)</f>
-        <v>259171.20000000001164</v>
+        <v>259081.79000000000815</v>
       </c>
       <c r="Q33" s="8"/>
       <c r="R33" s="101" t="s">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="S33" s="102">
         <f>SUM(S16:S32)</f>
-        <v>259171.20000000001164</v>
+        <v>259081.79000000000815</v>
       </c>
       <c r="T33" s="1"/>
       <c r="U33" s="57"/>
@@ -3351,7 +3351,7 @@
         <v>52</v>
       </c>
       <c r="J34" s="134">
-        <v>12725.72999999999956</v>
+        <v>0.0</v>
       </c>
       <c r="K34" s="106"/>
       <c r="L34" s="7"/>
@@ -3364,7 +3364,7 @@
         <v>51</v>
       </c>
       <c r="S34" s="133">
-        <v>12725.72999999999956</v>
+        <v>0.0</v>
       </c>
       <c r="T34" s="57"/>
       <c r="U34" s="110"/>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="J35" s="134">
         <f>J33-J34</f>
-        <v>246356.059999999997672</v>
+        <v>259081.79000000000815</v>
       </c>
       <c r="K35" s="106"/>
       <c r="L35" s="108"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S35" s="136">
         <f>S33-S34</f>
-        <v>246445.47000000000116</v>
+        <v>259081.79000000000815</v>
       </c>
       <c r="T35" s="1"/>
       <c r="U35" s="110"/>

--- a/public/uploads/invoice/ERS05071-Invoice1.xlsx
+++ b/public/uploads/invoice/ERS05071-Invoice1.xlsx
@@ -1295,22 +1295,22 @@
     <xf xfId="0" fontId="1" numFmtId="2" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="0" borderId="32" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="32" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="11" borderId="32" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="11" borderId="32" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="11" borderId="32" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="11" borderId="32" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="7" numFmtId="164" fillId="11" borderId="32" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="1" numFmtId="164" fillId="11" borderId="32" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="7" numFmtId="4" fillId="11" borderId="32" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="1" numFmtId="4" fillId="11" borderId="32" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="7" numFmtId="4" fillId="0" borderId="32" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="1" numFmtId="4" fillId="0" borderId="32" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="6" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">

--- a/public/uploads/invoice/ERS05071-Invoice1.xlsx
+++ b/public/uploads/invoice/ERS05071-Invoice1.xlsx
@@ -3236,35 +3236,35 @@
         <v>620.0</v>
       </c>
       <c r="I32" s="119">
-        <v>34.0</v>
+        <v>0</v>
       </c>
       <c r="J32" s="118">
-        <v>4216.0</v>
+        <v>0</v>
       </c>
       <c r="K32" s="119">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L32" s="118">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="M32" s="119">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N32" s="118">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O32" s="119">
-        <v>34.0</v>
+        <v>0</v>
       </c>
       <c r="P32" s="118">
-        <v>4216.0</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="120"/>
       <c r="R32" s="119">
-        <v>34.0</v>
+        <v>0</v>
       </c>
       <c r="S32" s="118">
-        <v>4216.0</v>
+        <v>0</v>
       </c>
       <c r="T32" s="1"/>
       <c r="U32" s="57"/>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="J33" s="94">
         <f>SUM(J16:J32)</f>
-        <v>259081.79000000000815</v>
+        <v>254865.79000000000815</v>
       </c>
       <c r="K33" s="95" t="s">
         <v>56</v>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="P33" s="100">
         <f>SUM(P16:P32)</f>
-        <v>259081.79000000000815</v>
+        <v>254865.79000000000815</v>
       </c>
       <c r="Q33" s="8"/>
       <c r="R33" s="101" t="s">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="S33" s="102">
         <f>SUM(S16:S32)</f>
-        <v>259081.79000000000815</v>
+        <v>254865.79000000000815</v>
       </c>
       <c r="T33" s="1"/>
       <c r="U33" s="57"/>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="J35" s="134">
         <f>J33-J34</f>
-        <v>259081.79000000000815</v>
+        <v>254865.79000000000815</v>
       </c>
       <c r="K35" s="106"/>
       <c r="L35" s="108"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S35" s="136">
         <f>S33-S34</f>
-        <v>259081.79000000000815</v>
+        <v>254865.79000000000815</v>
       </c>
       <c r="T35" s="1"/>
       <c r="U35" s="110"/>

--- a/public/uploads/invoice/ERS05071-Invoice1.xlsx
+++ b/public/uploads/invoice/ERS05071-Invoice1.xlsx
@@ -52,7 +52,7 @@
     <t>Lakeview Road Bridge</t>
   </si>
   <si>
-    <t>02/21/2026</t>
+    <t>02/24/2026</t>
   </si>
   <si>
     <t>1258 Willingham Dr</t>
@@ -214,18 +214,6 @@
     <t>CONC CURB &amp; GUTTER 8 IN X 30 IN TP 2</t>
   </si>
   <si>
-    <t>ADJUST MANHOLE TO GRADE</t>
-  </si>
-  <si>
-    <t>6 IN HEADER CURB</t>
-  </si>
-  <si>
-    <t>ADJUST WATER VALVE TO GRADE</t>
-  </si>
-  <si>
-    <t>BOND</t>
-  </si>
-  <si>
     <t>4 IN SIDEWALK $5 LOT</t>
   </si>
   <si>
@@ -235,7 +223,19 @@
     <t>6 IN DUMPSTER PAD (DOES NOT INCLUDE CATCH BASIN)</t>
   </si>
   <si>
+    <t>ADJUST MANHOLE TO GRADE</t>
+  </si>
+  <si>
+    <t>6 IN HEADER CURB</t>
+  </si>
+  <si>
     <t>6' CONCRETE SIDEWALK</t>
+  </si>
+  <si>
+    <t>ADJUST WATER VALVE TO GRADE</t>
+  </si>
+  <si>
+    <t>BOND</t>
   </si>
   <si>
     <t>CHANGE ORDER IN OCTOBER 2025</t>
@@ -256,10 +256,10 @@
     <t>LF</t>
   </si>
   <si>
-    <t>LS</t>
+    <t>SF</t>
   </si>
   <si>
-    <t>SF</t>
+    <t>LS</t>
   </si>
 </sst>
 </file>
@@ -2646,22 +2646,22 @@
       <c r="C22" s="115"/>
       <c r="D22" s="115"/>
       <c r="E22" s="117" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F22" s="118">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="G22" s="119">
-        <v>500.0</v>
+        <v>150.0</v>
       </c>
       <c r="H22" s="118">
-        <v>10000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="I22" s="119">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
       <c r="J22" s="118">
-        <v>1000.0</v>
+        <v>0.0</v>
       </c>
       <c r="K22" s="119">
         <v>0.0</v>
@@ -2676,17 +2676,17 @@
         <v>0.0</v>
       </c>
       <c r="O22" s="119">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
       <c r="P22" s="118">
-        <v>1000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q22" s="120"/>
       <c r="R22" s="119">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
       <c r="S22" s="118">
-        <v>1000.0</v>
+        <v>0.0</v>
       </c>
       <c r="T22" s="1"/>
       <c r="U22" s="57"/>
@@ -2713,19 +2713,19 @@
         <v>78</v>
       </c>
       <c r="F23" s="118">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="G23" s="119">
-        <v>523.0</v>
+        <v>120.0</v>
       </c>
       <c r="H23" s="118">
-        <v>10460.0</v>
+        <v>1200.0</v>
       </c>
       <c r="I23" s="119">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="J23" s="118">
-        <v>240.0</v>
+        <v>0.0</v>
       </c>
       <c r="K23" s="119">
         <v>0.0</v>
@@ -2740,17 +2740,17 @@
         <v>0.0</v>
       </c>
       <c r="O23" s="119">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="P23" s="118">
-        <v>240.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q23" s="120"/>
       <c r="R23" s="119">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="S23" s="118">
-        <v>240.0</v>
+        <v>0.0</v>
       </c>
       <c r="T23" s="1"/>
       <c r="U23" s="57"/>
@@ -2774,22 +2774,22 @@
       <c r="C24" s="115"/>
       <c r="D24" s="115"/>
       <c r="E24" s="117" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F24" s="118">
         <v>10.0</v>
       </c>
       <c r="G24" s="119">
-        <v>125.0</v>
+        <v>500.0</v>
       </c>
       <c r="H24" s="118">
-        <v>1250.0</v>
+        <v>5000.0</v>
       </c>
       <c r="I24" s="119">
-        <v>32.0</v>
+        <v>0.0</v>
       </c>
       <c r="J24" s="118">
-        <v>320.0</v>
+        <v>0.0</v>
       </c>
       <c r="K24" s="119">
         <v>0.0</v>
@@ -2804,17 +2804,17 @@
         <v>0.0</v>
       </c>
       <c r="O24" s="119">
-        <v>32.0</v>
+        <v>0.0</v>
       </c>
       <c r="P24" s="118">
-        <v>320.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q24" s="120"/>
       <c r="R24" s="119">
-        <v>32.0</v>
+        <v>0.0</v>
       </c>
       <c r="S24" s="118">
-        <v>320.0</v>
+        <v>0.0</v>
       </c>
       <c r="T24" s="1"/>
       <c r="U24" s="57"/>
@@ -2838,22 +2838,22 @@
       <c r="C25" s="115"/>
       <c r="D25" s="115"/>
       <c r="E25" s="117" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F25" s="118">
-        <v>-1823.75</v>
+        <v>20.0</v>
       </c>
       <c r="G25" s="119">
-        <v>1.0</v>
+        <v>500.0</v>
       </c>
       <c r="H25" s="118">
-        <v>-1823.75</v>
+        <v>10000.0</v>
       </c>
       <c r="I25" s="119">
-        <v>1.0</v>
+        <v>50.0</v>
       </c>
       <c r="J25" s="118">
-        <v>-1823.75</v>
+        <v>1000.0</v>
       </c>
       <c r="K25" s="119">
         <v>0.0</v>
@@ -2862,23 +2862,23 @@
         <v>0.0</v>
       </c>
       <c r="M25" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="N25" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O25" s="119">
-        <v>1.0</v>
+        <v>50.0</v>
       </c>
       <c r="P25" s="118">
-        <v>-1823.75</v>
+        <v>1000.0</v>
       </c>
       <c r="Q25" s="120"/>
       <c r="R25" s="119">
-        <v>1.0</v>
+        <v>50.0</v>
       </c>
       <c r="S25" s="118">
-        <v>-1823.75</v>
+        <v>1000.0</v>
       </c>
       <c r="T25" s="1"/>
       <c r="U25" s="57"/>
@@ -2902,47 +2902,47 @@
       <c r="C26" s="115"/>
       <c r="D26" s="115"/>
       <c r="E26" s="117" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F26" s="118">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="G26" s="119">
-        <v>150.0</v>
+        <v>523.0</v>
       </c>
       <c r="H26" s="118">
-        <v>1500.0</v>
+        <v>10460.0</v>
       </c>
       <c r="I26" s="119">
-        <v>0</v>
+        <v>12.0</v>
       </c>
       <c r="J26" s="118">
-        <v>0</v>
+        <v>240.0</v>
       </c>
       <c r="K26" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="L26" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M26" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="N26" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O26" s="119">
-        <v>0</v>
+        <v>12.0</v>
       </c>
       <c r="P26" s="118">
-        <v>0</v>
+        <v>240.0</v>
       </c>
       <c r="Q26" s="120"/>
       <c r="R26" s="119">
-        <v>0</v>
+        <v>12.0</v>
       </c>
       <c r="S26" s="118">
-        <v>0</v>
+        <v>240.0</v>
       </c>
       <c r="T26" s="1"/>
       <c r="U26" s="57"/>
@@ -2966,47 +2966,47 @@
       <c r="C27" s="115"/>
       <c r="D27" s="115"/>
       <c r="E27" s="117" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F27" s="118">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="G27" s="119">
-        <v>120.0</v>
+        <v>250.0</v>
       </c>
       <c r="H27" s="118">
-        <v>1200.0</v>
+        <v>3000.0</v>
       </c>
       <c r="I27" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="J27" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="K27" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="L27" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M27" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="N27" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O27" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="P27" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="Q27" s="120"/>
       <c r="R27" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="S27" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="T27" s="1"/>
       <c r="U27" s="57"/>
@@ -3030,47 +3030,47 @@
       <c r="C28" s="115"/>
       <c r="D28" s="115"/>
       <c r="E28" s="117" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F28" s="118">
         <v>10.0</v>
       </c>
       <c r="G28" s="119">
-        <v>500.0</v>
+        <v>125.0</v>
       </c>
       <c r="H28" s="118">
-        <v>5000.0</v>
+        <v>1250.0</v>
       </c>
       <c r="I28" s="119">
-        <v>0</v>
+        <v>32.0</v>
       </c>
       <c r="J28" s="118">
-        <v>0</v>
+        <v>320.0</v>
       </c>
       <c r="K28" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="L28" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M28" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="N28" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O28" s="119">
-        <v>0</v>
+        <v>32.0</v>
       </c>
       <c r="P28" s="118">
-        <v>0</v>
+        <v>320.0</v>
       </c>
       <c r="Q28" s="120"/>
       <c r="R28" s="119">
-        <v>0</v>
+        <v>32.0</v>
       </c>
       <c r="S28" s="118">
-        <v>0</v>
+        <v>320.0</v>
       </c>
       <c r="T28" s="1"/>
       <c r="U28" s="57"/>
@@ -3097,25 +3097,25 @@
         <v>80</v>
       </c>
       <c r="F29" s="118">
-        <v>12.0</v>
+        <v>-1823.75</v>
       </c>
       <c r="G29" s="119">
-        <v>250.0</v>
+        <v>1.0</v>
       </c>
       <c r="H29" s="118">
-        <v>3000.0</v>
+        <v>-1823.75</v>
       </c>
       <c r="I29" s="119">
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="J29" s="118">
-        <v>0</v>
+        <v>-1823.75</v>
       </c>
       <c r="K29" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="L29" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M29" s="119">
         <v>0</v>
@@ -3124,17 +3124,17 @@
         <v>0</v>
       </c>
       <c r="O29" s="119">
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="P29" s="118">
-        <v>0</v>
+        <v>-1823.75</v>
       </c>
       <c r="Q29" s="120"/>
       <c r="R29" s="119">
-        <v>0</v>
+        <v>1.0</v>
       </c>
       <c r="S29" s="118">
-        <v>0</v>
+        <v>-1823.75</v>
       </c>
       <c r="T29" s="1"/>
       <c r="U29" s="57"/>
@@ -3236,35 +3236,35 @@
         <v>620.0</v>
       </c>
       <c r="I32" s="119">
-        <v>0</v>
+        <v>34.0</v>
       </c>
       <c r="J32" s="118">
-        <v>0</v>
+        <v>4216.0</v>
       </c>
       <c r="K32" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="L32" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M32" s="119">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="N32" s="118">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O32" s="119">
-        <v>0</v>
+        <v>34.0</v>
       </c>
       <c r="P32" s="118">
-        <v>0</v>
+        <v>4216.0</v>
       </c>
       <c r="Q32" s="120"/>
       <c r="R32" s="119">
-        <v>0</v>
+        <v>34.0</v>
       </c>
       <c r="S32" s="118">
-        <v>0</v>
+        <v>4216.0</v>
       </c>
       <c r="T32" s="1"/>
       <c r="U32" s="57"/>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="J33" s="94">
         <f>SUM(J16:J32)</f>
-        <v>254865.79000000000815</v>
+        <v>259081.79000000000815</v>
       </c>
       <c r="K33" s="95" t="s">
         <v>56</v>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="P33" s="100">
         <f>SUM(P16:P32)</f>
-        <v>254865.79000000000815</v>
+        <v>259081.79000000000815</v>
       </c>
       <c r="Q33" s="8"/>
       <c r="R33" s="101" t="s">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="S33" s="102">
         <f>SUM(S16:S32)</f>
-        <v>254865.79000000000815</v>
+        <v>259081.79000000000815</v>
       </c>
       <c r="T33" s="1"/>
       <c r="U33" s="57"/>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="J35" s="134">
         <f>J33-J34</f>
-        <v>254865.79000000000815</v>
+        <v>259081.79000000000815</v>
       </c>
       <c r="K35" s="106"/>
       <c r="L35" s="108"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="S35" s="136">
         <f>S33-S34</f>
-        <v>254865.79000000000815</v>
+        <v>259081.79000000000815</v>
       </c>
       <c r="T35" s="1"/>
       <c r="U35" s="110"/>
